--- a/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_15_7.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste03/content/results/metrics_15_7.xlsx
@@ -513,661 +513,661 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_24</t>
+          <t>model_15_7_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9999359773155977</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7175853603376072</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9998433550125857</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9996508468463037</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9998232778020779</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G2" t="n">
-        <v>3.800663109720306e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1676535297808027</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0001379053030251096</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J2" t="n">
-        <v>9.960365575502246e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0001187547580502798</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002514487541925339</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M2" t="n">
-        <v>0.006164951832512811</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000056909052802</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00642740659523249</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P2" t="n">
-        <v>122.3554998218074</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q2" t="n">
-        <v>184.5181668900857</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_23</t>
+          <t>model_15_7_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9999364237404759</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7175775804527894</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9998447424145647</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9996523976614407</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9998245162116022</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G3" t="n">
-        <v>3.774161400494639e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.167658148256504</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000136683878110813</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J3" t="n">
-        <v>9.916125145362263e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0001179225647822178</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002508780338468012</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M3" t="n">
-        <v>0.006143420383218651</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000056512230688</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O3" t="n">
-        <v>0.006404958507565633</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P3" t="n">
-        <v>122.3694945050231</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q3" t="n">
-        <v>184.5321615733014</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_22</t>
+          <t>model_15_7_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9999369308726762</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7175680051349649</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D4" t="n">
-        <v>0.99984633779896</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9996541030681745</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9998259228437698</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G4" t="n">
-        <v>3.744055842385205e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1676638325787969</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001352793520412391</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J4" t="n">
-        <v>9.867474648167652e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0001169773283337864</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002502410704508548</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M4" t="n">
-        <v>0.006118869047777706</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N4" t="n">
-        <v>1.00005606144651</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O4" t="n">
-        <v>0.006379361970946696</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P4" t="n">
-        <v>122.3855119825982</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q4" t="n">
-        <v>184.5481790508765</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_21</t>
+          <t>model_15_7_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9999374707868425</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7175584787083411</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9998480142869076</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9996559921730948</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F5" t="n">
-        <v>0.999827422840965</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G5" t="n">
-        <v>3.712004205163985e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.167669487877161</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001338034249640538</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J5" t="n">
-        <v>9.81358375410808e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0001159693519386542</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002495533323896339</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M5" t="n">
-        <v>0.006092621935721914</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000055581522807</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006351997464991678</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P5" t="n">
-        <v>122.4027070343805</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q5" t="n">
-        <v>184.5653741026587</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_20</t>
+          <t>model_15_7_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9999380841005854</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7175467270862226</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9998499441434904</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9996580628452956</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9998291256366205</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G6" t="n">
-        <v>3.675595252014091e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1676764641476942</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000132104440137123</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J6" t="n">
-        <v>9.754513251983395e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0001148250979148257</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002487697151163883</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M6" t="n">
-        <v>0.006062668762198782</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N6" t="n">
-        <v>1.000055036355035</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O6" t="n">
-        <v>0.006320769122860048</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P6" t="n">
-        <v>122.422420744169</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q6" t="n">
-        <v>184.5850878124473</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_19</t>
+          <t>model_15_7_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9999387555763714</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7175338674308884</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9998520524912718</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9996603514317729</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9998309929505947</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G7" t="n">
-        <v>3.635733548731749e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1676840981946086</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000130248317292145</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J7" t="n">
-        <v>9.68922626338371e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001135702899629911</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002479026745785336</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M7" t="n">
-        <v>0.006029704427856932</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N7" t="n">
-        <v>1.00005443948767</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O7" t="n">
-        <v>0.006286401428559686</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P7" t="n">
-        <v>122.4442291455343</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q7" t="n">
-        <v>184.6068962138125</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_18</t>
+          <t>model_15_7_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9999394752150035</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7175205909304641</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9998542960263552</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9996628632138242</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9998329957309798</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G8" t="n">
-        <v>3.593012690851986e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1676919796987755</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0001282731798132233</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J8" t="n">
-        <v>9.617572127618516e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0001122244505447042</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002469583952177151</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M8" t="n">
-        <v>0.005994174414255883</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N8" t="n">
-        <v>1.000053799808886</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O8" t="n">
-        <v>0.006249358828722374</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P8" t="n">
-        <v>122.4678688494809</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q8" t="n">
-        <v>184.6305359177591</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_17</t>
+          <t>model_15_7_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9999402808764788</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7175051052178301</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D9" t="n">
-        <v>0.999856815901679</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9996656602845144</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9998352400836215</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G9" t="n">
-        <v>3.545185145398547e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>0.167701172686743</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0001260547611083721</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J9" t="n">
-        <v>9.537779502750054e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0001107162780679363</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002459034835612904</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M9" t="n">
-        <v>0.005954145736710303</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000053083665352</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O9" t="n">
-        <v>0.006207626047502892</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P9" t="n">
-        <v>122.4946701583142</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q9" t="n">
-        <v>184.6573372265925</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_16</t>
+          <t>model_15_7_15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9999411605297194</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7174875651729751</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9998595775215392</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9996686950671226</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F10" t="n">
-        <v>0.999837693247935</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G10" t="n">
-        <v>3.492965129132021e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1677115852150594</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0001236235181432912</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J10" t="n">
-        <v>9.451205619913473e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K10" t="n">
-        <v>0.000109067787171213</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L10" t="n">
-        <v>0.002447425819211413</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M10" t="n">
-        <v>0.005910131241463273</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000052301751361</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O10" t="n">
-        <v>0.006161737764070631</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P10" t="n">
-        <v>122.5243489645333</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q10" t="n">
-        <v>184.6870160328115</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_15</t>
+          <t>model_15_7_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9999421056039374</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7174692493464689</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9998625270901833</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9996720276580604</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9998403327411053</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G11" t="n">
-        <v>3.436861441045524e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.167722458280876</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0001210268110007439</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J11" t="n">
-        <v>9.356136096117681e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0001072940859809604</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L11" t="n">
-        <v>0.00243477622120001</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M11" t="n">
-        <v>0.00586247510958087</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N11" t="n">
-        <v>1.000051461685389</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O11" t="n">
-        <v>0.006112052811992202</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P11" t="n">
-        <v>122.556733563677</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q11" t="n">
-        <v>184.7194006319552</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_14</t>
+          <t>model_15_7_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9999431692169141</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7174465472673044</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9998658884517669</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9996756659156346</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9998433068602899</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G12" t="n">
-        <v>3.373720780180254e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1677359352157468</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0001180675743509612</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J12" t="n">
-        <v>9.252346755786171e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0001052955209544115</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L12" t="n">
-        <v>0.00242053593197722</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M12" t="n">
-        <v>0.005808373937842031</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000050516251632</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O12" t="n">
-        <v>0.006055648441367576</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P12" t="n">
-        <v>122.5938184811796</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q12" t="n">
-        <v>184.7564855494578</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_13</t>
+          <t>model_15_7_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9999443089465606</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7174223852041104</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9998694790776538</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9996796273379047</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9998465001748557</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G13" t="n">
-        <v>3.306061504983836e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1677502788602056</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I13" t="n">
-        <v>0.000114906500644491</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J13" t="n">
-        <v>9.139338428088344e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0001031496598056705</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L13" t="n">
-        <v>0.002405221079434528</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M13" t="n">
-        <v>0.005749836088954046</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000049503158613</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O13" t="n">
-        <v>0.005994618515062376</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P13" t="n">
-        <v>122.6343357233922</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q13" t="n">
-        <v>184.7970027916705</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="14">
@@ -1177,712 +1177,712 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9999455295379091</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C14" t="n">
-        <v>0.7173966026072496</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9998733098868793</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9996839501939059</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9998499262767566</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G14" t="n">
-        <v>3.233601929860108e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1677655845234523</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0001115339771069881</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J14" t="n">
-        <v>9.016019404198455e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K14" t="n">
-        <v>0.000100847368938493</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L14" t="n">
-        <v>0.002388252042539784</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M14" t="n">
-        <v>0.005686476879281326</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000048418188525</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O14" t="n">
-        <v>0.005928561972662243</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P14" t="n">
-        <v>122.6786576009769</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q14" t="n">
-        <v>184.8413246692552</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_11</t>
+          <t>model_15_7_10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9999468674772646</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C15" t="n">
-        <v>0.7173672994980771</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9998775176956659</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9996886999647606</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9998536920590558</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G15" t="n">
-        <v>3.154176070120277e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1677829801148855</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0001078295550544715</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J15" t="n">
-        <v>8.880521690338305e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K15" t="n">
-        <v>9.831681776232681e-05</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L15" t="n">
-        <v>0.002369318870244438</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M15" t="n">
-        <v>0.005616205186885783</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000047228909098</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O15" t="n">
-        <v>0.005855298668838965</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P15" t="n">
-        <v>122.7283963071987</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q15" t="n">
-        <v>184.8910633754769</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_10</t>
+          <t>model_15_7_9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9999482946745186</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7173353606039712</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9998820092592319</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9996938129161481</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9998577195391856</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G16" t="n">
-        <v>3.069451475947699e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1678019404221152</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0001038753242499126</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J16" t="n">
-        <v>8.734663448905393e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K16" t="n">
-        <v>9.561040943336944e-05</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L16" t="n">
-        <v>0.002348875158219413</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M16" t="n">
-        <v>0.005540263058689271</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N16" t="n">
-        <v>1.000045960289317</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O16" t="n">
-        <v>0.00577612352702325</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P16" t="n">
-        <v>122.7828531833293</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q16" t="n">
-        <v>184.9455202516076</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_9</t>
+          <t>model_15_7_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9999498850702694</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7172961142754066</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D17" t="n">
-        <v>0.999887070929908</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9996993866339173</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9998622174199217</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9750387140337e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1678252387381043</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I17" t="n">
-        <v>9.941918913870825e-05</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J17" t="n">
-        <v>8.575660827825476e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K17" t="n">
-        <v>9.258789870848151e-05</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L17" t="n">
-        <v>0.002325775626497973</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M17" t="n">
-        <v>0.005454391546298908</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N17" t="n">
-        <v>1.000044546604205</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O17" t="n">
-        <v>0.005686596286571894</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P17" t="n">
-        <v>122.8453368258735</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q17" t="n">
-        <v>185.0080038941517</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_8</t>
+          <t>model_15_7_7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.999951592934473</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C18" t="n">
-        <v>0.7172522394688927</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9998925194876049</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9997054155039391</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9998670676599366</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G18" t="n">
-        <v>2.873652517319648e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1678512847185439</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I18" t="n">
-        <v>9.462245090509168e-05</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J18" t="n">
-        <v>8.403673982545192e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K18" t="n">
-        <v>8.932860765033329e-05</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L18" t="n">
-        <v>0.002300387672229656</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M18" t="n">
-        <v>0.00536064596603772</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000043028502691</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O18" t="n">
-        <v>0.005588859762878883</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P18" t="n">
-        <v>122.9146831804364</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q18" t="n">
-        <v>185.0773502487146</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_7</t>
+          <t>model_15_7_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9999533747177932</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7172053003000991</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9998982098251783</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9997118046979548</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9998721498207954</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G19" t="n">
-        <v>2.767878162525622e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1678791498368062</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I19" t="n">
-        <v>8.961285729899274e-05</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J19" t="n">
-        <v>8.221408098775809e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K19" t="n">
-        <v>8.591346914337541e-05</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L19" t="n">
-        <v>0.002273272303755148</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M19" t="n">
-        <v>0.005261062784766612</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000041444695295</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O19" t="n">
-        <v>0.005485037119415461</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P19" t="n">
-        <v>122.9896888892243</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q19" t="n">
-        <v>185.1523559575026</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_6</t>
+          <t>model_15_7_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9999552753466263</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7171511933807841</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9999043246923062</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9997186139564748</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9998776007027965</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G20" t="n">
-        <v>2.655048624705118e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1679112700414088</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I20" t="n">
-        <v>8.422952127179218e-05</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J20" t="n">
-        <v>8.027158946395038e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K20" t="n">
-        <v>8.225055536787126e-05</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L20" t="n">
-        <v>0.002243547456381731</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M20" t="n">
-        <v>0.005152716394975681</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000039755247443</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O20" t="n">
-        <v>0.005372078199503184</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P20" t="n">
-        <v>123.0729249921083</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q20" t="n">
-        <v>185.2355920603866</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_5</t>
+          <t>model_15_7_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.999957234494273</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C21" t="n">
-        <v>0.7170926931753878</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9999106511739636</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E21" t="n">
-        <v>0.999725755319077</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9998832606955418</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G21" t="n">
-        <v>2.538745157324308e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1679459982904094</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I21" t="n">
-        <v>7.865988649158185e-05</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J21" t="n">
-        <v>7.823435790886738e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K21" t="n">
-        <v>7.844712220022462e-05</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L21" t="n">
-        <v>0.002212245966886106</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M21" t="n">
-        <v>0.005038596190730418</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000038013782868</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O21" t="n">
-        <v>0.00525309966190181</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P21" t="n">
-        <v>123.1625110771271</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q21" t="n">
-        <v>185.3251781454053</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_4</t>
+          <t>model_15_7_3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9999593652383921</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7170198228911755</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9999176545567476</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9997333202008951</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9998894539889207</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G22" t="n">
-        <v>2.412254982071501e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1679892572389502</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I22" t="n">
-        <v>7.249432932330586e-05</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J22" t="n">
-        <v>7.607630813484782e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K22" t="n">
-        <v>7.428531872907685e-05</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L22" t="n">
-        <v>0.00217717381082668</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M22" t="n">
-        <v>0.004911471248079847</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000036119788096</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O22" t="n">
-        <v>0.005120562747257694</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P22" t="n">
-        <v>123.2647269554652</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q22" t="n">
-        <v>185.4273940237435</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_3</t>
+          <t>model_15_7_2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9999615455256869</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7169426424463834</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9999248131599278</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9997413909553192</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9998958569012298</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G23" t="n">
-        <v>2.282823709900592e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1680350748850004</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I23" t="n">
-        <v>6.619212101714598e-05</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J23" t="n">
-        <v>7.377394701673922e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K23" t="n">
-        <v>6.99826543721127e-05</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L23" t="n">
-        <v>0.002138823612735934</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M23" t="n">
-        <v>0.004777890444433183</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000034181754945</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O23" t="n">
-        <v>0.004981295132249409</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P23" t="n">
-        <v>123.3750246380393</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q23" t="n">
-        <v>185.5376917063176</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_2</t>
+          <t>model_15_7_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9999637850593057</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C24" t="n">
-        <v>0.7168531481244235</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9999322964358804</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9997496637910731</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9999025142544747</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G24" t="n">
-        <v>2.149875320010742e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1680882025804692</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I24" t="n">
-        <v>5.960408104919881e-05</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J24" t="n">
-        <v>7.141393773190733e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K24" t="n">
-        <v>6.550900939055309e-05</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L24" t="n">
-        <v>0.00209815657959482</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M24" t="n">
-        <v>0.004636674799908596</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000032191058395</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O24" t="n">
-        <v>0.004834067645380726</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P24" t="n">
-        <v>123.4950312304097</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q24" t="n">
-        <v>185.657698298688</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_1</t>
+          <t>model_15_7_11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9999660408713662</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7167581650343864</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D25" t="n">
-        <v>0.999939848559519</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9997584610675386</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9999093285894701</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G25" t="n">
-        <v>2.015960571499811e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.168144588645771</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I25" t="n">
-        <v>5.295542975135643e-05</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J25" t="n">
-        <v>6.890432014037682e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K25" t="n">
-        <v>6.092987494586662e-05</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L25" t="n">
-        <v>0.002053038589779837</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M25" t="n">
-        <v>0.004489944956789349</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000030185892119</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O25" t="n">
-        <v>0.004681091209067244</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P25" t="n">
-        <v>123.6236593454803</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q25" t="n">
-        <v>185.7863264137586</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>model_15_7_0</t>
+          <t>model_15_7_24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9999682706689568</v>
+        <v>0.9998992775071769</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7166472899379979</v>
+        <v>0.6727811401712758</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9999475426763148</v>
+        <v>0.9999999999818717</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9997671249924371</v>
+        <v>0.9999999999999291</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9999162076318208</v>
+        <v>0.9999999999984037</v>
       </c>
       <c r="G26" t="n">
-        <v>1.88359015429697e-05</v>
+        <v>5.979322272492997e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1682104088925421</v>
+        <v>0.1942512503130713</v>
       </c>
       <c r="I26" t="n">
-        <v>4.618177215949471e-05</v>
+        <v>2.872819355693436e-12</v>
       </c>
       <c r="J26" t="n">
-        <v>6.643274403131219e-05</v>
+        <v>1.25263533322594e-13</v>
       </c>
       <c r="K26" t="n">
-        <v>5.630725809540345e-05</v>
+        <v>1.545375582284852e-12</v>
       </c>
       <c r="L26" t="n">
-        <v>0.002006304022776052</v>
+        <v>0.001961868165465913</v>
       </c>
       <c r="M26" t="n">
-        <v>0.004340034739834429</v>
+        <v>0.007732607757084926</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000028203849816</v>
+        <v>1.000089531104732</v>
       </c>
       <c r="O26" t="n">
-        <v>0.004524799003819624</v>
+        <v>0.008061800878008773</v>
       </c>
       <c r="P26" t="n">
-        <v>123.7594917053269</v>
+        <v>121.4492364715786</v>
       </c>
       <c r="Q26" t="n">
-        <v>185.9221587736051</v>
+        <v>183.6119035398569</v>
       </c>
     </row>
   </sheetData>
